--- a/Team-Data/2013-14/12-10-2013-14.xlsx
+++ b/Team-Data/2013-14/12-10-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,55 +728,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
         <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
       <c r="H2" t="n">
         <v>48</v>
       </c>
       <c r="I2" t="n">
-        <v>37.5</v>
+        <v>37.8</v>
       </c>
       <c r="J2" t="n">
-        <v>81.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.463</v>
       </c>
       <c r="L2" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O2" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="R2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="S2" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T2" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U2" t="n">
         <v>24.4</v>
@@ -718,34 +785,34 @@
         <v>14.7</v>
       </c>
       <c r="W2" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X2" t="n">
         <v>4.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="AA2" t="n">
         <v>19.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>99.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -754,13 +821,13 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL2" t="n">
         <v>11</v>
@@ -769,10 +836,10 @@
         <v>12</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
         <v>20</v>
@@ -784,7 +851,7 @@
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
         <v>27</v>
@@ -793,16 +860,16 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.435</v>
+        <v>0.455</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
@@ -864,64 +931,64 @@
         <v>80.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L3" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.361</v>
+        <v>0.353</v>
       </c>
       <c r="O3" t="n">
         <v>15.5</v>
       </c>
       <c r="P3" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R3" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S3" t="n">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>41.1</v>
+        <v>41.4</v>
       </c>
       <c r="U3" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="V3" t="n">
-        <v>16.1</v>
+        <v>16.4</v>
       </c>
       <c r="W3" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z3" t="n">
         <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.9</v>
+        <v>-0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>13</v>
@@ -930,7 +997,7 @@
         <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
         <v>23</v>
@@ -948,16 +1015,16 @@
         <v>22</v>
       </c>
       <c r="AM3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO3" t="n">
         <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
@@ -966,25 +1033,25 @@
         <v>22</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -1025,52 +1092,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
         <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="J4" t="n">
-        <v>78.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.437</v>
+        <v>0.431</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="O4" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P4" t="n">
         <v>26.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.753</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S4" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T4" t="n">
         <v>41.2</v>
@@ -1082,40 +1149,40 @@
         <v>14.5</v>
       </c>
       <c r="W4" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="X4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="AA4" t="n">
         <v>21.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>94.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7.1</v>
+        <v>-7.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF4" t="n">
         <v>25</v>
       </c>
       <c r="AG4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1124,19 +1191,19 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>25</v>
       </c>
       <c r="AM4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AN4" t="n">
         <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP4" t="n">
         <v>6</v>
@@ -1151,7 +1218,7 @@
         <v>23</v>
       </c>
       <c r="AT4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU4" t="n">
         <v>24</v>
@@ -1160,25 +1227,25 @@
         <v>7</v>
       </c>
       <c r="AW4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AY4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA4" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -1285,16 +1352,16 @@
         <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
         <v>13</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>23</v>
@@ -1333,10 +1400,10 @@
         <v>12</v>
       </c>
       <c r="AT5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
@@ -1345,13 +1412,13 @@
         <v>28</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -1389,91 +1456,91 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
         <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>0.421</v>
+        <v>0.444</v>
       </c>
       <c r="H6" t="n">
         <v>49.1</v>
       </c>
       <c r="I6" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="J6" t="n">
         <v>82.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.428</v>
+        <v>0.431</v>
       </c>
       <c r="L6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M6" t="n">
         <v>15.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.329</v>
+        <v>0.336</v>
       </c>
       <c r="O6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>22.6</v>
+        <v>23.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.776</v>
+        <v>0.781</v>
       </c>
       <c r="R6" t="n">
         <v>12.6</v>
       </c>
       <c r="S6" t="n">
-        <v>33.5</v>
+        <v>33.8</v>
       </c>
       <c r="T6" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="U6" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V6" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W6" t="n">
         <v>6.2</v>
       </c>
       <c r="X6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE6" t="n">
         <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
         <v>21</v>
@@ -1482,13 +1549,13 @@
         <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AJ6" t="n">
         <v>17</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1497,16 +1564,16 @@
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP6" t="n">
         <v>14</v>
       </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
@@ -1515,31 +1582,31 @@
         <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AY6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC6" t="n">
         <v>15</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0.381</v>
+        <v>0.35</v>
       </c>
       <c r="H7" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I7" t="n">
-        <v>35.3</v>
+        <v>35</v>
       </c>
       <c r="J7" t="n">
-        <v>83.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.421</v>
+        <v>0.415</v>
       </c>
       <c r="L7" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M7" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.348</v>
+        <v>0.342</v>
       </c>
       <c r="O7" t="n">
         <v>15.8</v>
@@ -1610,67 +1677,67 @@
         <v>21.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="U7" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="V7" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="AD7" t="n">
         <v>16</v>
       </c>
-      <c r="W7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>13</v>
-      </c>
       <c r="AE7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
         <v>6</v>
       </c>
       <c r="AI7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
         <v>21</v>
@@ -1688,7 +1755,7 @@
         <v>22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR7" t="n">
         <v>10</v>
@@ -1697,31 +1764,31 @@
         <v>16</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AV7" t="n">
         <v>21</v>
       </c>
       <c r="AW7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX7" t="n">
         <v>17</v>
       </c>
-      <c r="AX7" t="n">
-        <v>19</v>
-      </c>
       <c r="AY7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA7" t="n">
         <v>23</v>
       </c>
       <c r="BB7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1852,7 +1919,7 @@
         <v>7</v>
       </c>
       <c r="AK8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL8" t="n">
         <v>8</v>
@@ -1864,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
         <v>24</v>
@@ -1885,25 +1952,25 @@
         <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
         <v>6</v>
       </c>
       <c r="AX8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
         <v>26</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>8</v>
@@ -2034,16 +2101,16 @@
         <v>6</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="n">
         <v>11</v>
@@ -2058,7 +2125,7 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>5</v>
@@ -2070,7 +2137,7 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
         <v>6</v>
@@ -2079,7 +2146,7 @@
         <v>23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>12</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -2117,118 +2184,118 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>0.455</v>
+        <v>0.476</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J10" t="n">
         <v>84.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L10" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.318</v>
+        <v>0.32</v>
       </c>
       <c r="O10" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.672</v>
+        <v>0.677</v>
       </c>
       <c r="R10" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T10" t="n">
-        <v>44.1</v>
+        <v>44.4</v>
       </c>
       <c r="U10" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="W10" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X10" t="n">
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
         <v>13</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AN10" t="n">
         <v>28</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP10" t="n">
         <v>9</v>
@@ -2240,22 +2307,22 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>22</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2264,13 +2331,13 @@
         <v>11</v>
       </c>
       <c r="BA10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
         <v>16</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2437,10 +2504,10 @@
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
         <v>26</v>
@@ -2449,10 +2516,10 @@
         <v>15</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>6.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2625,7 +2692,7 @@
         <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2730,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>0.864</v>
+        <v>0.857</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J13" t="n">
-        <v>79.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.453</v>
+        <v>0.451</v>
       </c>
       <c r="L13" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M13" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O13" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="R13" t="n">
         <v>10.1</v>
@@ -2717,31 +2784,31 @@
         <v>20.8</v>
       </c>
       <c r="V13" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="W13" t="n">
         <v>7.4</v>
       </c>
       <c r="X13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z13" t="n">
         <v>19.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2762,13 +2829,13 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM13" t="n">
         <v>19</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>20</v>
       </c>
       <c r="AN13" t="n">
         <v>12</v>
@@ -2777,7 +2844,7 @@
         <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2789,31 +2856,31 @@
         <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW13" t="n">
         <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC13" t="n">
         <v>2</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>7</v>
@@ -2935,7 +3002,7 @@
         <v>7</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>8</v>
@@ -2944,16 +3011,16 @@
         <v>16</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
         <v>6</v>
@@ -2971,7 +3038,7 @@
         <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -2980,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>21</v>
@@ -2989,7 +3056,7 @@
         <v>2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
@@ -3045,85 +3112,85 @@
         <v>37.9</v>
       </c>
       <c r="J15" t="n">
-        <v>85.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
       <c r="L15" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="R15" t="n">
         <v>10.3</v>
       </c>
-      <c r="M15" t="n">
-        <v>26</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="O15" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="R15" t="n">
-        <v>10.1</v>
-      </c>
       <c r="S15" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="T15" t="n">
-        <v>43</v>
+        <v>43.6</v>
       </c>
       <c r="U15" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="V15" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
         <v>7</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.3</v>
+        <v>101</v>
       </c>
       <c r="AC15" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>13</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
         <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK15" t="n">
         <v>19</v>
@@ -3135,13 +3202,13 @@
         <v>2</v>
       </c>
       <c r="AN15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP15" t="n">
         <v>27</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>25</v>
       </c>
       <c r="AQ15" t="n">
         <v>24</v>
@@ -3150,16 +3217,16 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>25</v>
@@ -3168,19 +3235,19 @@
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB15" t="n">
         <v>14</v>
       </c>
       <c r="BC15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3296,10 +3363,10 @@
         <v>11</v>
       </c>
       <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
         <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>11</v>
       </c>
       <c r="AI16" t="n">
         <v>21</v>
@@ -3308,7 +3375,7 @@
         <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,22 +3384,22 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>23</v>
       </c>
       <c r="AP16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ16" t="n">
         <v>10</v>
       </c>
       <c r="AR16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT16" t="n">
         <v>21</v>
@@ -3344,7 +3411,7 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX16" t="n">
         <v>27</v>
@@ -3353,13 +3420,13 @@
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -3391,70 +3458,70 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.727</v>
+        <v>0.762</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="J17" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.504</v>
+        <v>0.508</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="M17" t="n">
         <v>21.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.386</v>
+        <v>0.395</v>
       </c>
       <c r="O17" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="P17" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.762</v>
+        <v>0.765</v>
       </c>
       <c r="R17" t="n">
         <v>6.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="V17" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="W17" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X17" t="n">
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Z17" t="n">
         <v>20.7</v>
@@ -3463,13 +3530,13 @@
         <v>21.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.6</v>
+        <v>103.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3493,13 +3560,13 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM17" t="n">
         <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO17" t="n">
         <v>8</v>
@@ -3523,10 +3590,10 @@
         <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX17" t="n">
         <v>8</v>
@@ -3541,7 +3608,7 @@
         <v>11</v>
       </c>
       <c r="BB17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
         <v>3</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -3573,58 +3640,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.238</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I18" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="J18" t="n">
-        <v>81.40000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.418</v>
+        <v>0.419</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>0.371</v>
+        <v>0.376</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P18" t="n">
         <v>19.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R18" t="n">
         <v>10.5</v>
       </c>
       <c r="S18" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="T18" t="n">
         <v>39.9</v>
       </c>
       <c r="U18" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="V18" t="n">
         <v>16.4</v>
@@ -3633,28 +3700,28 @@
         <v>6.9</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>90.2</v>
+        <v>90.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8</v>
+        <v>-8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF18" t="n">
         <v>29</v>
@@ -3666,25 +3733,25 @@
         <v>6</v>
       </c>
       <c r="AI18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
@@ -3693,7 +3760,7 @@
         <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS18" t="n">
         <v>27</v>
@@ -3702,10 +3769,10 @@
         <v>28</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
         <v>26</v>
@@ -3714,13 +3781,13 @@
         <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -3755,115 +3822,115 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
         <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>0.476</v>
+        <v>0.45</v>
       </c>
       <c r="H19" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J19" t="n">
-        <v>89</v>
+        <v>89.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.426</v>
+        <v>0.423</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M19" t="n">
         <v>24</v>
       </c>
       <c r="N19" t="n">
-        <v>0.329</v>
+        <v>0.323</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="P19" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.803</v>
+        <v>0.8</v>
       </c>
       <c r="R19" t="n">
         <v>13.3</v>
       </c>
       <c r="S19" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="T19" t="n">
         <v>45.4</v>
       </c>
       <c r="U19" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="V19" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W19" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.5</v>
+        <v>104.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>17</v>
       </c>
       <c r="AI19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
         <v>27</v>
       </c>
       <c r="AL19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM19" t="n">
         <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3878,19 +3945,19 @@
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>6</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3902,13 +3969,13 @@
         <v>2</v>
       </c>
       <c r="BA19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -4015,10 +4082,10 @@
         <v>0.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
@@ -4039,19 +4106,19 @@
         <v>17</v>
       </c>
       <c r="AL20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM20" t="n">
         <v>27</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
         <v>13</v>
       </c>
       <c r="AP20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ20" t="n">
         <v>9</v>
@@ -4060,7 +4127,7 @@
         <v>2</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
         <v>12</v>
@@ -4072,22 +4139,22 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA20" t="n">
         <v>16</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
         <v>13</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -4119,91 +4186,91 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>0.25</v>
+        <v>0.263</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>36.1</v>
+        <v>35.8</v>
       </c>
       <c r="J21" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.432</v>
+        <v>0.43</v>
       </c>
       <c r="L21" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M21" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O21" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="P21" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="Q21" t="n">
         <v>0.77</v>
       </c>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
       </c>
       <c r="T21" t="n">
-        <v>39</v>
+        <v>39.4</v>
       </c>
       <c r="U21" t="n">
-        <v>20.1</v>
+        <v>19.7</v>
       </c>
       <c r="V21" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="AB21" t="n">
         <v>94.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-4.4</v>
+        <v>-3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
         <v>28</v>
       </c>
       <c r="AF21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG21" t="n">
         <v>28</v>
@@ -4218,7 +4285,7 @@
         <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
         <v>6</v>
@@ -4242,7 +4309,7 @@
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
         <v>29</v>
@@ -4254,19 +4321,19 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA21" t="n">
         <v>28</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>29</v>
       </c>
       <c r="BB21" t="n">
         <v>24</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8</v>
+        <v>0.789</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
@@ -4319,40 +4386,40 @@
         <v>38.3</v>
       </c>
       <c r="J22" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L22" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M22" t="n">
         <v>18.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.331</v>
+        <v>0.336</v>
       </c>
       <c r="O22" t="n">
         <v>21.9</v>
       </c>
       <c r="P22" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="R22" t="n">
         <v>11.2</v>
       </c>
       <c r="S22" t="n">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="T22" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="U22" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="V22" t="n">
         <v>16.3</v>
@@ -4364,25 +4431,25 @@
         <v>6.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.6</v>
+        <v>104.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4400,7 +4467,7 @@
         <v>15</v>
       </c>
       <c r="AK22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL22" t="n">
         <v>26</v>
@@ -4409,7 +4476,7 @@
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
         <v>2</v>
@@ -4418,7 +4485,7 @@
         <v>5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>14</v>
@@ -4430,19 +4497,19 @@
         <v>2</v>
       </c>
       <c r="AU22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW22" t="n">
         <v>17</v>
       </c>
-      <c r="AV22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>16</v>
-      </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
         <v>22</v>
@@ -4451,7 +4518,7 @@
         <v>14</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -4561,28 +4628,28 @@
         <v>-4.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG23" t="n">
         <v>27</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="n">
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>15</v>
@@ -4591,7 +4658,7 @@
         <v>16</v>
       </c>
       <c r="AN23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO23" t="n">
         <v>20</v>
@@ -4618,16 +4685,16 @@
         <v>26</v>
       </c>
       <c r="AW23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY23" t="n">
         <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>-7.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH24" t="n">
         <v>1</v>
@@ -4761,7 +4828,7 @@
         <v>2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK24" t="n">
         <v>18</v>
@@ -4776,10 +4843,10 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4791,7 +4858,7 @@
         <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
         <v>9</v>
@@ -4809,16 +4876,16 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>0.571</v>
+        <v>0.55</v>
       </c>
       <c r="H25" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38</v>
+        <v>37.7</v>
       </c>
       <c r="J25" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.465</v>
+        <v>0.462</v>
       </c>
       <c r="L25" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="O25" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P25" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.745</v>
+        <v>0.738</v>
       </c>
       <c r="R25" t="n">
         <v>10.7</v>
@@ -4898,19 +4965,19 @@
         <v>41.7</v>
       </c>
       <c r="U25" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="V25" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z25" t="n">
         <v>21.2</v>
@@ -4919,16 +4986,16 @@
         <v>20.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>101.8</v>
+        <v>101.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF25" t="n">
         <v>9</v>
@@ -4940,13 +5007,13 @@
         <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>5</v>
@@ -4961,16 +5028,16 @@
         <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AR25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT25" t="n">
         <v>19</v>
@@ -4979,22 +5046,22 @@
         <v>26</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
         <v>10</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ25" t="n">
         <v>18</v>
       </c>
       <c r="BA25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -5107,10 +5174,10 @@
         <v>6.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>2</v>
@@ -5119,16 +5186,16 @@
         <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
         <v>4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>4</v>
@@ -5146,7 +5213,7 @@
         <v>19</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR26" t="n">
         <v>5</v>
@@ -5158,7 +5225,7 @@
         <v>7</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>10</v>
@@ -5310,16 +5377,16 @@
         <v>8</v>
       </c>
       <c r="AK27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM27" t="n">
         <v>13</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
         <v>9</v>
@@ -5328,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR27" t="n">
         <v>11</v>
@@ -5337,7 +5404,7 @@
         <v>17</v>
       </c>
       <c r="AT27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU27" t="n">
         <v>16</v>
@@ -5364,7 +5431,7 @@
         <v>17</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8</v>
+        <v>0.789</v>
       </c>
       <c r="H28" t="n">
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>40.9</v>
+        <v>40.6</v>
       </c>
       <c r="J28" t="n">
         <v>83.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.491</v>
+        <v>0.488</v>
       </c>
       <c r="L28" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.406</v>
+        <v>0.397</v>
       </c>
       <c r="O28" t="n">
         <v>12.3</v>
@@ -5432,19 +5499,19 @@
         <v>16.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="R28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>42</v>
+        <v>42.3</v>
       </c>
       <c r="U28" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="V28" t="n">
         <v>14.7</v>
@@ -5462,19 +5529,19 @@
         <v>17.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.6</v>
+        <v>101.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF28" t="n">
         <v>2</v>
@@ -5495,13 +5562,13 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5525,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY28" t="n">
         <v>8</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -5575,61 +5642,61 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
         <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>0.35</v>
+        <v>0.368</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J29" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.429</v>
+        <v>0.427</v>
       </c>
       <c r="L29" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="M29" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0.334</v>
+        <v>0.328</v>
       </c>
       <c r="O29" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P29" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.782</v>
+        <v>0.778</v>
       </c>
       <c r="R29" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S29" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T29" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U29" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="V29" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="W29" t="n">
         <v>7.1</v>
@@ -5638,97 +5705,97 @@
         <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z29" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AA29" t="n">
         <v>22.9</v>
       </c>
-      <c r="AA29" t="n">
-        <v>22.7</v>
-      </c>
       <c r="AB29" t="n">
-        <v>98</v>
+        <v>97.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.3</v>
+        <v>-0.7</v>
       </c>
       <c r="AD29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE29" t="n">
         <v>22</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
         <v>14</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP29" t="n">
         <v>8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
         <v>7</v>
       </c>
       <c r="AS29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU29" t="n">
         <v>30</v>
       </c>
       <c r="AV29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>18</v>
       </c>
       <c r="AZ29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF30" t="n">
         <v>30</v>
@@ -5856,7 +5923,7 @@
         <v>23</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>27</v>
@@ -5865,22 +5932,22 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP30" t="n">
         <v>16</v>
       </c>
-      <c r="AP30" t="n">
-        <v>15</v>
-      </c>
       <c r="AQ30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT30" t="n">
         <v>25</v>
@@ -5904,7 +5971,7 @@
         <v>23</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
         <v>19</v>
@@ -6053,13 +6120,13 @@
         <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
         <v>18</v>
@@ -6071,28 +6138,28 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW31" t="n">
         <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-10-2013-14</t>
+          <t>2013-12-10</t>
         </is>
       </c>
     </row>
